--- a/output/yearly_total_coral_cover_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_37_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252097887323378</v>
+        <v>1.248210166414561</v>
       </c>
       <c r="C3" t="n">
-        <v>4.660471107601167</v>
+        <v>4.601487705530019</v>
       </c>
       <c r="D3" t="n">
-        <v>6.019767765849243</v>
+        <v>6.035505181548319</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93233676077379</v>
+        <v>11.8852030534929</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.367937282786626</v>
+        <v>1.358952589956958</v>
       </c>
       <c r="C4" t="n">
-        <v>5.211931851447609</v>
+        <v>5.097129495391271</v>
       </c>
       <c r="D4" t="n">
-        <v>6.216501477423511</v>
+        <v>6.36588516294185</v>
       </c>
       <c r="E4" t="n">
-        <v>12.79637061165775</v>
+        <v>12.82196724829008</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.530744232186378</v>
+        <v>1.513028104937688</v>
       </c>
       <c r="C5" t="n">
-        <v>5.924579056210661</v>
+        <v>5.71933008105466</v>
       </c>
       <c r="D5" t="n">
-        <v>6.465531668244423</v>
+        <v>6.673476579757353</v>
       </c>
       <c r="E5" t="n">
-        <v>13.92085495664146</v>
+        <v>13.9058347657497</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.71018976863517</v>
+        <v>1.689502256358454</v>
       </c>
       <c r="C6" t="n">
-        <v>6.788019084505548</v>
+        <v>6.4819082118419</v>
       </c>
       <c r="D6" t="n">
-        <v>6.759105667361593</v>
+        <v>7.071303756110721</v>
       </c>
       <c r="E6" t="n">
-        <v>15.25731452050231</v>
+        <v>15.24271422431108</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.924229484292915</v>
+        <v>1.897272127723654</v>
       </c>
       <c r="C7" t="n">
-        <v>7.7888551069854</v>
+        <v>7.386421777278234</v>
       </c>
       <c r="D7" t="n">
-        <v>7.040535521371428</v>
+        <v>7.451224507818202</v>
       </c>
       <c r="E7" t="n">
-        <v>16.75362011264974</v>
+        <v>16.73491841282009</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.164426949176762</v>
+        <v>1.165090500301559</v>
       </c>
       <c r="C8" t="n">
-        <v>5.469063208577674</v>
+        <v>5.059178826220044</v>
       </c>
       <c r="D8" t="n">
-        <v>5.212298998587727</v>
+        <v>5.656230010616262</v>
       </c>
       <c r="E8" t="n">
-        <v>11.84578915634216</v>
+        <v>11.88049933713786</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.453904071140946</v>
+        <v>1.491939702369071</v>
       </c>
       <c r="C9" t="n">
-        <v>6.843352834838227</v>
+        <v>6.212343136572644</v>
       </c>
       <c r="D9" t="n">
-        <v>5.706014811168742</v>
+        <v>6.221788169591751</v>
       </c>
       <c r="E9" t="n">
-        <v>14.00327171714791</v>
+        <v>13.92607100853347</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.760389411565739</v>
+        <v>1.835914920826319</v>
       </c>
       <c r="C10" t="n">
-        <v>8.458742105293572</v>
+        <v>7.540523090533901</v>
       </c>
       <c r="D10" t="n">
-        <v>6.211525510373309</v>
+        <v>6.742041993167073</v>
       </c>
       <c r="E10" t="n">
-        <v>16.43065702723262</v>
+        <v>16.11848000452729</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.08173210711236</v>
+        <v>2.186971431110075</v>
       </c>
       <c r="C11" t="n">
-        <v>10.25796286561342</v>
+        <v>8.984419829850673</v>
       </c>
       <c r="D11" t="n">
-        <v>6.660297206386445</v>
+        <v>7.266094819872765</v>
       </c>
       <c r="E11" t="n">
-        <v>18.99999217911222</v>
+        <v>18.43748608083351</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.396335329706902</v>
+        <v>2.539337733580437</v>
       </c>
       <c r="C12" t="n">
-        <v>12.13251922534936</v>
+        <v>10.544457571508</v>
       </c>
       <c r="D12" t="n">
-        <v>7.096054149940263</v>
+        <v>7.751008787465619</v>
       </c>
       <c r="E12" t="n">
-        <v>21.62490870499653</v>
+        <v>20.83480409255405</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.680773576672904</v>
+        <v>2.881277771374658</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04801150503255</v>
+        <v>12.14768690606102</v>
       </c>
       <c r="D13" t="n">
-        <v>7.560700334214263</v>
+        <v>8.272766957435948</v>
       </c>
       <c r="E13" t="n">
-        <v>24.28948541591971</v>
+        <v>23.30173163487163</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.534687646232699</v>
+        <v>1.639656110770768</v>
       </c>
       <c r="C14" t="n">
-        <v>9.778148229435978</v>
+        <v>8.540429446260896</v>
       </c>
       <c r="D14" t="n">
-        <v>5.795217428260752</v>
+        <v>6.282223194429424</v>
       </c>
       <c r="E14" t="n">
-        <v>17.10805330392943</v>
+        <v>16.46230875146109</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.553350670090431</v>
+        <v>1.688468606625919</v>
       </c>
       <c r="C15" t="n">
-        <v>10.72556421646528</v>
+        <v>9.261434777736795</v>
       </c>
       <c r="D15" t="n">
-        <v>5.780893729255792</v>
+        <v>6.313531128717855</v>
       </c>
       <c r="E15" t="n">
-        <v>18.0598086158115</v>
+        <v>17.26343451308057</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.786289947877072</v>
+        <v>1.964987665004076</v>
       </c>
       <c r="C16" t="n">
-        <v>12.77481528692486</v>
+        <v>10.94539716240022</v>
       </c>
       <c r="D16" t="n">
-        <v>6.214364793111884</v>
+        <v>6.819111561450879</v>
       </c>
       <c r="E16" t="n">
-        <v>20.77547002791381</v>
+        <v>19.72949638885518</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.422248081665312</v>
+        <v>1.583470689656723</v>
       </c>
       <c r="C17" t="n">
-        <v>11.83540054368517</v>
+        <v>10.08737912131964</v>
       </c>
       <c r="D17" t="n">
-        <v>5.752845197345459</v>
+        <v>6.338752227239957</v>
       </c>
       <c r="E17" t="n">
-        <v>19.01049382269594</v>
+        <v>18.00960203821632</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.610095687395897</v>
+        <v>1.807142269115274</v>
       </c>
       <c r="C18" t="n">
-        <v>13.8650362950139</v>
+        <v>11.75730251381234</v>
       </c>
       <c r="D18" t="n">
-        <v>6.146732193766322</v>
+        <v>6.786007028863675</v>
       </c>
       <c r="E18" t="n">
-        <v>21.62186417617612</v>
+        <v>20.35045181179128</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.602546047550238</v>
+        <v>1.809518098559551</v>
       </c>
       <c r="C19" t="n">
-        <v>14.86544702311844</v>
+        <v>12.55802575887308</v>
       </c>
       <c r="D19" t="n">
-        <v>6.212332575364095</v>
+        <v>6.899722865446584</v>
       </c>
       <c r="E19" t="n">
-        <v>22.68032564603277</v>
+        <v>21.26726672287921</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.777336408814341</v>
+        <v>2.007261721148944</v>
       </c>
       <c r="C20" t="n">
-        <v>17.08859506443126</v>
+        <v>14.47528085049667</v>
       </c>
       <c r="D20" t="n">
-        <v>6.635691637866446</v>
+        <v>7.309877421326816</v>
       </c>
       <c r="E20" t="n">
-        <v>25.50162311111204</v>
+        <v>23.79241999297243</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.052227371934689</v>
+        <v>1.187944174569768</v>
       </c>
       <c r="C21" t="n">
-        <v>12.51816680208066</v>
+        <v>10.66635501242215</v>
       </c>
       <c r="D21" t="n">
-        <v>5.536340376127911</v>
+        <v>6.105606782435424</v>
       </c>
       <c r="E21" t="n">
-        <v>19.10673455014325</v>
+        <v>17.95990596942735</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_37_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.248210166414561</v>
+        <v>1.250134391914884</v>
       </c>
       <c r="C3" t="n">
-        <v>4.601487705530019</v>
+        <v>4.671947738263813</v>
       </c>
       <c r="D3" t="n">
-        <v>6.035505181548319</v>
+        <v>6.127328044326524</v>
       </c>
       <c r="E3" t="n">
-        <v>11.8852030534929</v>
+        <v>12.04941017450522</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.358952589956958</v>
+        <v>1.373866585542723</v>
       </c>
       <c r="C4" t="n">
-        <v>5.097129495391271</v>
+        <v>5.229792666110868</v>
       </c>
       <c r="D4" t="n">
-        <v>6.36588516294185</v>
+        <v>6.357438814512049</v>
       </c>
       <c r="E4" t="n">
-        <v>12.82196724829008</v>
+        <v>12.96109806616564</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.513028104937688</v>
+        <v>1.541970159524213</v>
       </c>
       <c r="C5" t="n">
-        <v>5.71933008105466</v>
+        <v>5.957998852951548</v>
       </c>
       <c r="D5" t="n">
-        <v>6.673476579757353</v>
+        <v>6.645847643658591</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9058347657497</v>
+        <v>14.14581665613435</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.689502256358454</v>
+        <v>1.730958912276995</v>
       </c>
       <c r="C6" t="n">
-        <v>6.4819082118419</v>
+        <v>6.835772454813009</v>
       </c>
       <c r="D6" t="n">
-        <v>7.071303756110721</v>
+        <v>6.960598652470485</v>
       </c>
       <c r="E6" t="n">
-        <v>15.24271422431108</v>
+        <v>15.52733001956049</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.897272127723654</v>
+        <v>1.941147114933023</v>
       </c>
       <c r="C7" t="n">
-        <v>7.386421777278234</v>
+        <v>7.847490012848703</v>
       </c>
       <c r="D7" t="n">
-        <v>7.451224507818202</v>
+        <v>7.3346882197015</v>
       </c>
       <c r="E7" t="n">
-        <v>16.73491841282009</v>
+        <v>17.12332534748323</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.165090500301559</v>
+        <v>1.164885044793809</v>
       </c>
       <c r="C8" t="n">
-        <v>5.059178826220044</v>
+        <v>5.440950363270304</v>
       </c>
       <c r="D8" t="n">
-        <v>5.656230010616262</v>
+        <v>5.561959182658599</v>
       </c>
       <c r="E8" t="n">
-        <v>11.88049933713786</v>
+        <v>12.16779459072271</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.491939702369071</v>
+        <v>1.443384126979101</v>
       </c>
       <c r="C9" t="n">
-        <v>6.212343136572644</v>
+        <v>6.709499051627821</v>
       </c>
       <c r="D9" t="n">
-        <v>6.221788169591751</v>
+        <v>6.010003453926885</v>
       </c>
       <c r="E9" t="n">
-        <v>13.92607100853347</v>
+        <v>14.16288663253381</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.835914920826319</v>
+        <v>1.729805863116082</v>
       </c>
       <c r="C10" t="n">
-        <v>7.540523090533901</v>
+        <v>8.155567231100983</v>
       </c>
       <c r="D10" t="n">
-        <v>6.742041993167073</v>
+        <v>6.488008617536408</v>
       </c>
       <c r="E10" t="n">
-        <v>16.11848000452729</v>
+        <v>16.37338171175347</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.186971431110075</v>
+        <v>2.021894637108411</v>
       </c>
       <c r="C11" t="n">
-        <v>8.984419829850673</v>
+        <v>9.714099215738708</v>
       </c>
       <c r="D11" t="n">
-        <v>7.266094819872765</v>
+        <v>6.945958240005755</v>
       </c>
       <c r="E11" t="n">
-        <v>18.43748608083351</v>
+        <v>18.68195209285287</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.539337733580437</v>
+        <v>2.323895094776852</v>
       </c>
       <c r="C12" t="n">
-        <v>10.544457571508</v>
+        <v>11.39075116754514</v>
       </c>
       <c r="D12" t="n">
-        <v>7.751008787465619</v>
+        <v>7.403170568353135</v>
       </c>
       <c r="E12" t="n">
-        <v>20.83480409255405</v>
+        <v>21.11781683067512</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.881277771374658</v>
+        <v>2.611599248904003</v>
       </c>
       <c r="C13" t="n">
-        <v>12.14768690606102</v>
+        <v>13.09742905120605</v>
       </c>
       <c r="D13" t="n">
-        <v>8.272766957435948</v>
+        <v>7.885997839055523</v>
       </c>
       <c r="E13" t="n">
-        <v>23.30173163487163</v>
+        <v>23.59502613916558</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.639656110770768</v>
+        <v>1.516721663244982</v>
       </c>
       <c r="C14" t="n">
-        <v>8.540429446260896</v>
+        <v>9.195598776690003</v>
       </c>
       <c r="D14" t="n">
-        <v>6.282223194429424</v>
+        <v>5.985676482884632</v>
       </c>
       <c r="E14" t="n">
-        <v>16.46230875146109</v>
+        <v>16.69799692281962</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.688468606625919</v>
+        <v>1.544053519331213</v>
       </c>
       <c r="C15" t="n">
-        <v>9.261434777736795</v>
+        <v>9.952634248911762</v>
       </c>
       <c r="D15" t="n">
-        <v>6.313531128717855</v>
+        <v>5.986255714030138</v>
       </c>
       <c r="E15" t="n">
-        <v>17.26343451308057</v>
+        <v>17.48294348227311</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.964987665004076</v>
+        <v>1.786996806224129</v>
       </c>
       <c r="C16" t="n">
-        <v>10.94539716240022</v>
+        <v>11.75681163996021</v>
       </c>
       <c r="D16" t="n">
-        <v>6.819111561450879</v>
+        <v>6.423634133749135</v>
       </c>
       <c r="E16" t="n">
-        <v>19.72949638885518</v>
+        <v>19.96744257993348</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.583470689656723</v>
+        <v>1.43437266581276</v>
       </c>
       <c r="C17" t="n">
-        <v>10.08737912131964</v>
+        <v>10.77672308933358</v>
       </c>
       <c r="D17" t="n">
-        <v>6.338752227239957</v>
+        <v>5.945041945405858</v>
       </c>
       <c r="E17" t="n">
-        <v>18.00960203821632</v>
+        <v>18.1561377005522</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.807142269115274</v>
+        <v>1.634825912065873</v>
       </c>
       <c r="C18" t="n">
-        <v>11.75730251381234</v>
+        <v>12.53308936718521</v>
       </c>
       <c r="D18" t="n">
-        <v>6.786007028863675</v>
+        <v>6.363796611175292</v>
       </c>
       <c r="E18" t="n">
-        <v>20.35045181179128</v>
+        <v>20.53171189042637</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.809518098559551</v>
+        <v>1.63823257659961</v>
       </c>
       <c r="C19" t="n">
-        <v>12.55802575887308</v>
+        <v>13.34570157694438</v>
       </c>
       <c r="D19" t="n">
-        <v>6.899722865446584</v>
+        <v>6.447412063145994</v>
       </c>
       <c r="E19" t="n">
-        <v>21.26726672287921</v>
+        <v>21.43134621668998</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.007261721148944</v>
+        <v>1.817489889918035</v>
       </c>
       <c r="C20" t="n">
-        <v>14.47528085049667</v>
+        <v>15.30734148227697</v>
       </c>
       <c r="D20" t="n">
-        <v>7.309877421326816</v>
+        <v>6.935448664404126</v>
       </c>
       <c r="E20" t="n">
-        <v>23.79241999297243</v>
+        <v>24.06028003659913</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.187944174569768</v>
+        <v>1.07733066073228</v>
       </c>
       <c r="C21" t="n">
-        <v>10.66635501242215</v>
+        <v>11.19885496720562</v>
       </c>
       <c r="D21" t="n">
-        <v>6.105606782435424</v>
+        <v>5.79791723444743</v>
       </c>
       <c r="E21" t="n">
-        <v>17.95990596942735</v>
+        <v>18.07410286238533</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_37_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.250134391914884</v>
+        <v>2.58155419758573</v>
       </c>
       <c r="C3" t="n">
-        <v>4.671947738263813</v>
+        <v>7.698587776702804</v>
       </c>
       <c r="D3" t="n">
-        <v>6.127328044326524</v>
+        <v>8.124117137332457</v>
       </c>
       <c r="E3" t="n">
-        <v>12.04941017450522</v>
+        <v>18.40425911162099</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.373866585542723</v>
+        <v>1.047829691721722</v>
       </c>
       <c r="C4" t="n">
-        <v>5.229792666110868</v>
+        <v>4.447782651433219</v>
       </c>
       <c r="D4" t="n">
-        <v>6.357438814512049</v>
+        <v>5.717080819611688</v>
       </c>
       <c r="E4" t="n">
-        <v>12.96109806616564</v>
+        <v>11.21269316276663</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.541970159524213</v>
+        <v>1.114527962765277</v>
       </c>
       <c r="C5" t="n">
-        <v>5.957998852951548</v>
+        <v>5.012746327548868</v>
       </c>
       <c r="D5" t="n">
-        <v>6.645847643658591</v>
+        <v>6.022203718381768</v>
       </c>
       <c r="E5" t="n">
-        <v>14.14581665613435</v>
+        <v>12.14947800869591</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.730958912276995</v>
+        <v>1.204004484937646</v>
       </c>
       <c r="C6" t="n">
-        <v>6.835772454813009</v>
+        <v>5.735693146894979</v>
       </c>
       <c r="D6" t="n">
-        <v>6.960598652470485</v>
+        <v>6.311446370746904</v>
       </c>
       <c r="E6" t="n">
-        <v>15.52733001956049</v>
+        <v>13.25114400257953</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.941147114933023</v>
+        <v>1.303883390169646</v>
       </c>
       <c r="C7" t="n">
-        <v>7.847490012848703</v>
+        <v>6.634182631313248</v>
       </c>
       <c r="D7" t="n">
-        <v>7.3346882197015</v>
+        <v>6.623648634942161</v>
       </c>
       <c r="E7" t="n">
-        <v>17.12332534748323</v>
+        <v>14.56171465642506</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.164885044793809</v>
+        <v>1.4094122233879</v>
       </c>
       <c r="C8" t="n">
-        <v>5.440950363270304</v>
+        <v>7.690948770691242</v>
       </c>
       <c r="D8" t="n">
-        <v>5.561959182658599</v>
+        <v>6.934082931149494</v>
       </c>
       <c r="E8" t="n">
-        <v>12.16779459072271</v>
+        <v>16.03444392522864</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.443384126979101</v>
+        <v>1.525020251208954</v>
       </c>
       <c r="C9" t="n">
-        <v>6.709499051627821</v>
+        <v>8.884584212006089</v>
       </c>
       <c r="D9" t="n">
-        <v>6.010003453926885</v>
+        <v>7.259779641654268</v>
       </c>
       <c r="E9" t="n">
-        <v>14.16288663253381</v>
+        <v>17.66938410486931</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.729805863116082</v>
+        <v>0.9719105922502573</v>
       </c>
       <c r="C10" t="n">
-        <v>8.155567231100983</v>
+        <v>6.626581019171035</v>
       </c>
       <c r="D10" t="n">
-        <v>6.488008617536408</v>
+        <v>5.70336511305142</v>
       </c>
       <c r="E10" t="n">
-        <v>16.37338171175347</v>
+        <v>13.30185672447271</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.021894637108411</v>
+        <v>0.9110716870180824</v>
       </c>
       <c r="C11" t="n">
-        <v>9.714099215738708</v>
+        <v>7.014292822532186</v>
       </c>
       <c r="D11" t="n">
-        <v>6.945958240005755</v>
+        <v>5.500388775198392</v>
       </c>
       <c r="E11" t="n">
-        <v>18.68195209285287</v>
+        <v>13.42575328474866</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.323895094776852</v>
+        <v>0.9837602870405164</v>
       </c>
       <c r="C12" t="n">
-        <v>11.39075116754514</v>
+        <v>8.315383420016399</v>
       </c>
       <c r="D12" t="n">
-        <v>7.403170568353135</v>
+        <v>5.821675528890203</v>
       </c>
       <c r="E12" t="n">
-        <v>21.11781683067512</v>
+        <v>15.12081923594712</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.611599248904003</v>
+        <v>0.78102938611355</v>
       </c>
       <c r="C13" t="n">
-        <v>13.09742905120605</v>
+        <v>7.953854827927511</v>
       </c>
       <c r="D13" t="n">
-        <v>7.885997839055523</v>
+        <v>5.249228260020931</v>
       </c>
       <c r="E13" t="n">
-        <v>23.59502613916558</v>
+        <v>13.98411247406199</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.516721663244982</v>
+        <v>0.8517741256815753</v>
       </c>
       <c r="C14" t="n">
-        <v>9.195598776690003</v>
+        <v>9.351932281114268</v>
       </c>
       <c r="D14" t="n">
-        <v>5.985676482884632</v>
+        <v>5.582138906531024</v>
       </c>
       <c r="E14" t="n">
-        <v>16.69799692281962</v>
+        <v>15.78584531332687</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.544053519331213</v>
+        <v>0.8306469150861838</v>
       </c>
       <c r="C15" t="n">
-        <v>9.952634248911762</v>
+        <v>10.14475245715582</v>
       </c>
       <c r="D15" t="n">
-        <v>5.986255714030138</v>
+        <v>5.593772616826349</v>
       </c>
       <c r="E15" t="n">
-        <v>17.48294348227311</v>
+        <v>16.56917198906836</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.786996806224129</v>
+        <v>0.9186311443407831</v>
       </c>
       <c r="C16" t="n">
-        <v>11.75681163996021</v>
+        <v>11.93691325630429</v>
       </c>
       <c r="D16" t="n">
-        <v>6.423634133749135</v>
+        <v>5.973070842362104</v>
       </c>
       <c r="E16" t="n">
-        <v>19.96744257993348</v>
+        <v>18.82861524300717</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.43437266581276</v>
+        <v>0.5597140011451915</v>
       </c>
       <c r="C17" t="n">
-        <v>10.77672308933358</v>
+        <v>9.016508360481302</v>
       </c>
       <c r="D17" t="n">
-        <v>5.945041945405858</v>
+        <v>4.937238657088337</v>
       </c>
       <c r="E17" t="n">
-        <v>18.1561377005522</v>
+        <v>14.51346101871483</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.634825912065873</v>
+        <v>0.4434358030541994</v>
       </c>
       <c r="C18" t="n">
-        <v>12.53308936718521</v>
+        <v>8.076308219078216</v>
       </c>
       <c r="D18" t="n">
-        <v>6.363796611175292</v>
+        <v>4.451096828899401</v>
       </c>
       <c r="E18" t="n">
-        <v>20.53171189042637</v>
+        <v>12.97084085103182</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.63823257659961</v>
+        <v>0.5219461669628167</v>
       </c>
       <c r="C19" t="n">
-        <v>13.34570157694438</v>
+        <v>10.0534106507527</v>
       </c>
       <c r="D19" t="n">
-        <v>6.447412063145994</v>
+        <v>4.931681965082301</v>
       </c>
       <c r="E19" t="n">
-        <v>21.43134621668998</v>
+        <v>15.50703878279781</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.817489889918035</v>
+        <v>0.5942715203346792</v>
       </c>
       <c r="C20" t="n">
-        <v>15.30734148227697</v>
+        <v>12.12593895927997</v>
       </c>
       <c r="D20" t="n">
-        <v>6.935448664404126</v>
+        <v>5.372928470756029</v>
       </c>
       <c r="E20" t="n">
-        <v>24.06028003659913</v>
+        <v>18.09313895037068</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.07733066073228</v>
+        <v>0.6599995291340032</v>
       </c>
       <c r="C21" t="n">
-        <v>11.19885496720562</v>
+        <v>14.28365351610474</v>
       </c>
       <c r="D21" t="n">
-        <v>5.79791723444743</v>
+        <v>5.827389300528919</v>
       </c>
       <c r="E21" t="n">
-        <v>18.07410286238533</v>
+        <v>20.77104234576766</v>
       </c>
     </row>
   </sheetData>
